--- a/storage/Formato Reporte consumo mensual Intellectus MARZO - ABRIL.xlsx
+++ b/storage/Formato Reporte consumo mensual Intellectus MARZO - ABRIL.xlsx
@@ -397,16 +397,592 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:J19"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>REPORTE DE CONSUMO MENSUAL</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>20/03/2026, 12:21</v>
+      </c>
+      <c r="C2" t="str">
+        <v>MTRE. HERRERA</v>
+      </c>
+      <c r="D2" t="str">
+        <v>AT&amp;T</v>
+      </c>
+      <c r="E2" t="str">
+        <v>GEO</v>
+      </c>
+      <c r="F2" t="str">
+        <v>COCEFI</v>
+      </c>
+      <c r="G2">
+        <v>1000</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>998</v>
+      </c>
+      <c r="J2" t="str">
+        <v>POSITIVO</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>20/03/2026, 11:59</v>
+      </c>
+      <c r="C3" t="str">
+        <v>MTRE. HERRERA</v>
+      </c>
+      <c r="D3" t="str">
+        <v>TELCEL</v>
+      </c>
+      <c r="E3" t="str">
+        <v>GEO</v>
+      </c>
+      <c r="F3" t="str">
+        <v>COCEFI</v>
+      </c>
+      <c r="G3">
+        <v>998</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>997</v>
+      </c>
+      <c r="J3" t="str">
+        <v>POSITIVO</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>20/03/2026, 12:01</v>
+      </c>
+      <c r="C4" t="str">
+        <v>MTRE. HERRERA</v>
+      </c>
+      <c r="D4" t="str">
+        <v>TELCEL</v>
+      </c>
+      <c r="E4" t="str">
+        <v>GEO</v>
+      </c>
+      <c r="F4" t="str">
+        <v>COCEFI</v>
+      </c>
+      <c r="G4">
+        <v>997</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>996</v>
+      </c>
+      <c r="J4" t="str">
+        <v>POSITIVO</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>20/03/2026, 12:03</v>
+      </c>
+      <c r="C5" t="str">
+        <v>MTRE. HERRERA</v>
+      </c>
+      <c r="D5" t="str">
+        <v>TELCEL</v>
+      </c>
+      <c r="E5" t="str">
+        <v>GEO</v>
+      </c>
+      <c r="F5" t="str">
+        <v>COCEFI</v>
+      </c>
+      <c r="G5">
+        <v>996</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>995</v>
+      </c>
+      <c r="J5" t="str">
+        <v>POSITIVO</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="str">
+        <v>20/03/2026, 12:03</v>
+      </c>
+      <c r="C6" t="str">
+        <v>MTRE. HERRERA</v>
+      </c>
+      <c r="D6" t="str">
+        <v>TELCEL</v>
+      </c>
+      <c r="E6" t="str">
+        <v>GEO</v>
+      </c>
+      <c r="F6" t="str">
+        <v>COCEFI</v>
+      </c>
+      <c r="G6">
+        <v>996</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>995</v>
+      </c>
+      <c r="J6" t="str">
+        <v>POSITIVO</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="str">
+        <v>20/03/2026, 12:03</v>
+      </c>
+      <c r="C7" t="str">
+        <v>MTRE. HERRERA</v>
+      </c>
+      <c r="D7" t="str">
+        <v>TELCEL</v>
+      </c>
+      <c r="E7" t="str">
+        <v>GEO</v>
+      </c>
+      <c r="F7" t="str">
+        <v>COCEFI</v>
+      </c>
+      <c r="G7">
+        <v>996</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>995</v>
+      </c>
+      <c r="J7" t="str">
+        <v>POSITIVO</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8" t="str">
+        <v>20/03/2026, 12:03</v>
+      </c>
+      <c r="C8" t="str">
+        <v>MTRE. HERRERA</v>
+      </c>
+      <c r="D8" t="str">
+        <v>TELCEL</v>
+      </c>
+      <c r="E8" t="str">
+        <v>GEO</v>
+      </c>
+      <c r="F8" t="str">
+        <v>COCEFI</v>
+      </c>
+      <c r="G8">
+        <v>996</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>995</v>
+      </c>
+      <c r="J8" t="str">
+        <v>POSITIVO</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>4</v>
+      </c>
+      <c r="B9" t="str">
+        <v>20/03/2026, 12:03</v>
+      </c>
+      <c r="C9" t="str">
+        <v>MTRE. HERRERA</v>
+      </c>
+      <c r="D9" t="str">
+        <v>TELCEL</v>
+      </c>
+      <c r="E9" t="str">
+        <v>GEO</v>
+      </c>
+      <c r="F9" t="str">
+        <v>COCEFI</v>
+      </c>
+      <c r="G9">
+        <v>996</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>995</v>
+      </c>
+      <c r="J9" t="str">
+        <v>POSITIVO</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>4</v>
+      </c>
+      <c r="B10" t="str">
+        <v>20/03/2026, 12:03</v>
+      </c>
+      <c r="C10" t="str">
+        <v>MTRE. HERRERA</v>
+      </c>
+      <c r="D10" t="str">
+        <v>TELCEL</v>
+      </c>
+      <c r="E10" t="str">
+        <v>GEO</v>
+      </c>
+      <c r="F10" t="str">
+        <v>COCEFI</v>
+      </c>
+      <c r="G10">
+        <v>996</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>995</v>
+      </c>
+      <c r="J10" t="str">
+        <v>POSITIVO</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>4</v>
+      </c>
+      <c r="B11" t="str">
+        <v>20/03/2026, 12:03</v>
+      </c>
+      <c r="C11" t="str">
+        <v>MTRE. HERRERA</v>
+      </c>
+      <c r="D11" t="str">
+        <v>TELCEL</v>
+      </c>
+      <c r="E11" t="str">
+        <v>GEO</v>
+      </c>
+      <c r="F11" t="str">
+        <v>COCEFI</v>
+      </c>
+      <c r="G11">
+        <v>996</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>995</v>
+      </c>
+      <c r="J11" t="str">
+        <v>POSITIVO</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>4</v>
+      </c>
+      <c r="B12" t="str">
+        <v>20/03/2026, 12:03</v>
+      </c>
+      <c r="C12" t="str">
+        <v>MTRE. HERRERA</v>
+      </c>
+      <c r="D12" t="str">
+        <v>TELCEL</v>
+      </c>
+      <c r="E12" t="str">
+        <v>GEO</v>
+      </c>
+      <c r="F12" t="str">
+        <v>COCEFI</v>
+      </c>
+      <c r="G12">
+        <v>996</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>995</v>
+      </c>
+      <c r="J12" t="str">
+        <v>POSITIVO</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>5</v>
+      </c>
+      <c r="B13" t="str">
+        <v>20/03/2026, 11:55</v>
+      </c>
+      <c r="C13" t="str">
+        <v>MTRE. HERRERA</v>
+      </c>
+      <c r="D13" t="str">
+        <v>TELCEL</v>
+      </c>
+      <c r="E13" t="str">
+        <v>GEO</v>
+      </c>
+      <c r="F13" t="str">
+        <v>COCEFI</v>
+      </c>
+      <c r="G13">
+        <v>995</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>994</v>
+      </c>
+      <c r="J13" t="str">
+        <v>POSITIVO</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>6</v>
+      </c>
+      <c r="B14" t="str">
+        <v>20/03/2026, 10:17</v>
+      </c>
+      <c r="C14" t="str">
+        <v>MTRE. HERRERA</v>
+      </c>
+      <c r="D14" t="str">
+        <v>ALTAN</v>
+      </c>
+      <c r="E14" t="str">
+        <v>GEO</v>
+      </c>
+      <c r="F14" t="str">
+        <v>COCEFI</v>
+      </c>
+      <c r="G14">
+        <v>994</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>993</v>
+      </c>
+      <c r="J14" t="str">
+        <v>POSITIVO</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>7</v>
+      </c>
+      <c r="B15" t="str">
+        <v>20/03/2026, 12:00</v>
+      </c>
+      <c r="C15" t="str">
+        <v>TTE ABARCA</v>
+      </c>
+      <c r="D15" t="str">
+        <v>TELCEL</v>
+      </c>
+      <c r="E15" t="str">
+        <v>GEO</v>
+      </c>
+      <c r="F15" t="str">
+        <v>COCEFI</v>
+      </c>
+      <c r="G15">
+        <v>993</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>992</v>
+      </c>
+      <c r="J15" t="str">
+        <v>POSITIVO</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>8</v>
+      </c>
+      <c r="B16" t="str">
+        <v>20/03/2026, 10:47</v>
+      </c>
+      <c r="C16" t="str">
+        <v>MTRE MELCHOR</v>
+      </c>
+      <c r="D16" t="str">
+        <v>TELCEL</v>
+      </c>
+      <c r="E16" t="str">
+        <v>GEO</v>
+      </c>
+      <c r="F16" t="str">
+        <v>COCEFI</v>
+      </c>
+      <c r="G16">
+        <v>992</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>991</v>
+      </c>
+      <c r="J16" t="str">
+        <v>POSITIVO</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>9</v>
+      </c>
+      <c r="B17" t="str">
+        <v>20/03/2026, 16:16</v>
+      </c>
+      <c r="C17" t="str">
+        <v>CABO VELAZQUEZ</v>
+      </c>
+      <c r="D17" t="str">
+        <v>TELCEL</v>
+      </c>
+      <c r="E17" t="str">
+        <v>GEO</v>
+      </c>
+      <c r="F17" t="str">
+        <v>CEREGINA-3</v>
+      </c>
+      <c r="G17">
+        <v>991</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17">
+        <v>990</v>
+      </c>
+      <c r="J17" t="str">
+        <v>POSITIVO</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>10</v>
+      </c>
+      <c r="B18" t="str">
+        <v>20/03/2026, 10:47</v>
+      </c>
+      <c r="C18" t="str">
+        <v>CABO VELAZQUEZ</v>
+      </c>
+      <c r="D18" t="str">
+        <v>TELCEL</v>
+      </c>
+      <c r="E18" t="str">
+        <v>GEO</v>
+      </c>
+      <c r="F18" t="str">
+        <v>CEREGINA-3</v>
+      </c>
+      <c r="G18">
+        <v>990</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18">
+        <v>989</v>
+      </c>
+      <c r="J18" t="str">
+        <v>POSITIVO</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>11</v>
+      </c>
+      <c r="B19" t="str">
+        <v>21/03/2026, 09:57</v>
+      </c>
+      <c r="C19" t="str">
+        <v>CABO VELAZQUEZ</v>
+      </c>
+      <c r="D19" t="str">
+        <v>TELCEL</v>
+      </c>
+      <c r="E19" t="str">
+        <v>GEO</v>
+      </c>
+      <c r="F19" t="str">
+        <v>LANCEROS</v>
+      </c>
+      <c r="G19">
+        <v>989</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19">
+        <v>988</v>
+      </c>
+      <c r="J19" t="str">
+        <v>NEGATIVO</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J19"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/storage/Formato Reporte consumo mensual Intellectus MARZO - ABRIL.xlsx
+++ b/storage/Formato Reporte consumo mensual Intellectus MARZO - ABRIL.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J25"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -758,10 +758,10 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B13" t="str">
-        <v>20/03/2026, 11:55</v>
+        <v>20/03/2026, 12:03</v>
       </c>
       <c r="C13" t="str">
         <v>MTRE. HERRERA</v>
@@ -776,13 +776,13 @@
         <v>COCEFI</v>
       </c>
       <c r="G13">
+        <v>996</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
         <v>995</v>
-      </c>
-      <c r="H13">
-        <v>1</v>
-      </c>
-      <c r="I13">
-        <v>994</v>
       </c>
       <c r="J13" t="str">
         <v>POSITIVO</v>
@@ -790,16 +790,16 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B14" t="str">
-        <v>20/03/2026, 10:17</v>
+        <v>20/03/2026, 12:03</v>
       </c>
       <c r="C14" t="str">
         <v>MTRE. HERRERA</v>
       </c>
       <c r="D14" t="str">
-        <v>ALTAN</v>
+        <v>TELCEL</v>
       </c>
       <c r="E14" t="str">
         <v>GEO</v>
@@ -808,13 +808,13 @@
         <v>COCEFI</v>
       </c>
       <c r="G14">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="H14">
         <v>1</v>
       </c>
       <c r="I14">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="J14" t="str">
         <v>POSITIVO</v>
@@ -822,13 +822,13 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B15" t="str">
-        <v>20/03/2026, 12:00</v>
+        <v>20/03/2026, 12:03</v>
       </c>
       <c r="C15" t="str">
-        <v>TTE ABARCA</v>
+        <v>MTRE. HERRERA</v>
       </c>
       <c r="D15" t="str">
         <v>TELCEL</v>
@@ -840,13 +840,13 @@
         <v>COCEFI</v>
       </c>
       <c r="G15">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="H15">
         <v>1</v>
       </c>
       <c r="I15">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="J15" t="str">
         <v>POSITIVO</v>
@@ -854,13 +854,13 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B16" t="str">
-        <v>20/03/2026, 10:47</v>
+        <v>20/03/2026, 11:55</v>
       </c>
       <c r="C16" t="str">
-        <v>MTRE MELCHOR</v>
+        <v>MTRE. HERRERA</v>
       </c>
       <c r="D16" t="str">
         <v>TELCEL</v>
@@ -872,13 +872,13 @@
         <v>COCEFI</v>
       </c>
       <c r="G16">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="H16">
         <v>1</v>
       </c>
       <c r="I16">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="J16" t="str">
         <v>POSITIVO</v>
@@ -886,31 +886,31 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B17" t="str">
-        <v>20/03/2026, 16:16</v>
+        <v>20/03/2026, 10:17</v>
       </c>
       <c r="C17" t="str">
-        <v>CABO VELAZQUEZ</v>
+        <v>MTRE. HERRERA</v>
       </c>
       <c r="D17" t="str">
-        <v>TELCEL</v>
+        <v>ALTAN</v>
       </c>
       <c r="E17" t="str">
         <v>GEO</v>
       </c>
       <c r="F17" t="str">
-        <v>CEREGINA-3</v>
+        <v>COCEFI</v>
       </c>
       <c r="G17">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="H17">
         <v>1</v>
       </c>
       <c r="I17">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="J17" t="str">
         <v>POSITIVO</v>
@@ -918,13 +918,13 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B18" t="str">
-        <v>20/03/2026, 10:47</v>
+        <v>20/03/2026, 12:00</v>
       </c>
       <c r="C18" t="str">
-        <v>CABO VELAZQUEZ</v>
+        <v>TTE ABARCA</v>
       </c>
       <c r="D18" t="str">
         <v>TELCEL</v>
@@ -933,16 +933,16 @@
         <v>GEO</v>
       </c>
       <c r="F18" t="str">
-        <v>CEREGINA-3</v>
+        <v>COCEFI</v>
       </c>
       <c r="G18">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="H18">
         <v>1</v>
       </c>
       <c r="I18">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="J18" t="str">
         <v>POSITIVO</v>
@@ -950,39 +950,231 @@
     </row>
     <row r="19">
       <c r="A19">
+        <v>8</v>
+      </c>
+      <c r="B19" t="str">
+        <v>20/03/2026, 10:47</v>
+      </c>
+      <c r="C19" t="str">
+        <v>MTRE MELCHOR</v>
+      </c>
+      <c r="D19" t="str">
+        <v>TELCEL</v>
+      </c>
+      <c r="E19" t="str">
+        <v>GEO</v>
+      </c>
+      <c r="F19" t="str">
+        <v>COCEFI</v>
+      </c>
+      <c r="G19">
+        <v>992</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19">
+        <v>991</v>
+      </c>
+      <c r="J19" t="str">
+        <v>POSITIVO</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>9</v>
+      </c>
+      <c r="B20" t="str">
+        <v>20/03/2026, 16:16</v>
+      </c>
+      <c r="C20" t="str">
+        <v>CABO VELAZQUEZ</v>
+      </c>
+      <c r="D20" t="str">
+        <v>TELCEL</v>
+      </c>
+      <c r="E20" t="str">
+        <v>GEO</v>
+      </c>
+      <c r="F20" t="str">
+        <v>CEREGINA-3</v>
+      </c>
+      <c r="G20">
+        <v>991</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20">
+        <v>990</v>
+      </c>
+      <c r="J20" t="str">
+        <v>POSITIVO</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>10</v>
+      </c>
+      <c r="B21" t="str">
+        <v>20/03/2026, 10:47</v>
+      </c>
+      <c r="C21" t="str">
+        <v>CABO VELAZQUEZ</v>
+      </c>
+      <c r="D21" t="str">
+        <v>TELCEL</v>
+      </c>
+      <c r="E21" t="str">
+        <v>GEO</v>
+      </c>
+      <c r="F21" t="str">
+        <v>CEREGINA-3</v>
+      </c>
+      <c r="G21">
+        <v>990</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21">
+        <v>989</v>
+      </c>
+      <c r="J21" t="str">
+        <v>POSITIVO</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
         <v>11</v>
       </c>
-      <c r="B19" t="str">
+      <c r="B22" t="str">
         <v>21/03/2026, 09:57</v>
       </c>
-      <c r="C19" t="str">
+      <c r="C22" t="str">
         <v>CABO VELAZQUEZ</v>
       </c>
-      <c r="D19" t="str">
-        <v>TELCEL</v>
-      </c>
-      <c r="E19" t="str">
-        <v>GEO</v>
-      </c>
-      <c r="F19" t="str">
+      <c r="D22" t="str">
+        <v>TELCEL</v>
+      </c>
+      <c r="E22" t="str">
+        <v>GEO</v>
+      </c>
+      <c r="F22" t="str">
         <v>LANCEROS</v>
       </c>
-      <c r="G19">
+      <c r="G22">
         <v>989</v>
       </c>
-      <c r="H19">
-        <v>1</v>
-      </c>
-      <c r="I19">
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22">
         <v>988</v>
       </c>
-      <c r="J19" t="str">
+      <c r="J22" t="str">
         <v>NEGATIVO</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>12</v>
+      </c>
+      <c r="B23" t="str">
+        <v>10/02/2026, 11:38</v>
+      </c>
+      <c r="C23" t="str">
+        <v>CABO VELAZQUEZ</v>
+      </c>
+      <c r="D23" t="str">
+        <v>TELCEL</v>
+      </c>
+      <c r="E23" t="str">
+        <v>GEO</v>
+      </c>
+      <c r="F23" t="str">
+        <v>SO</v>
+      </c>
+      <c r="G23">
+        <v>1000</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>999</v>
+      </c>
+      <c r="J23" t="str">
+        <v>POSITIVO</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>13</v>
+      </c>
+      <c r="B24" t="str">
+        <v>10/02/2026, 14:07</v>
+      </c>
+      <c r="C24" t="str">
+        <v>CABO VELAZQUEZ</v>
+      </c>
+      <c r="D24" t="str">
+        <v>TELCEL</v>
+      </c>
+      <c r="E24" t="str">
+        <v>GEO</v>
+      </c>
+      <c r="F24" t="str">
+        <v>SO</v>
+      </c>
+      <c r="G24">
+        <v>999</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>998</v>
+      </c>
+      <c r="J24" t="str">
+        <v>POSITIVO</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>14</v>
+      </c>
+      <c r="B25" t="str">
+        <v>10/02/2026, 08:02</v>
+      </c>
+      <c r="C25" t="str">
+        <v>CABO GALICIA</v>
+      </c>
+      <c r="D25" t="str">
+        <v>TELCEL</v>
+      </c>
+      <c r="E25" t="str">
+        <v>GEO</v>
+      </c>
+      <c r="F25" t="str">
+        <v>SO</v>
+      </c>
+      <c r="G25">
+        <v>998</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25">
+        <v>997</v>
+      </c>
+      <c r="J25" t="str">
+        <v>POSITIVO</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J25"/>
   </ignoredErrors>
 </worksheet>
 </file>